--- a/data/outgame.xlsx
+++ b/data/outgame.xlsx
@@ -16,7 +16,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="대화이벤트" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요청" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="제작" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="읽어보기" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="오브젝트" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PX" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="읽어보기" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -434,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -835,6 +837,216 @@
       <c r="C26" t="inlineStr">
         <is>
           <t>오염·점검 날짜 난수 시드 [임시]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>fatigue_start</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>20</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>시작 피로도 0~100 (높을수록 피곤) [임시]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>fatigue_awake_per_hour</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>깨어 있을 때 시간당 피로 증가 [임시]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>fatigue_work_per_hour</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>업무·청소·지시 중 시간당 피로 증가 [임시]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>fatigue_train_per_hour</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>7</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>훈련 중 시간당 피로 증가 [임시]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fatigue_battle</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>20</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>전투 한 번 참가 시 피로 증가 [임시]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>hungry_fatigue</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>6</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>식사 시간에 식재료가 없으면 피로 증가 [임시]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>food_start</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>10</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>시작 식재료 (1 = 한 끼) [임시]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>food_pack_price</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>20</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>식재료 한 묶음 가격 USD [임시]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>food_pack_amount</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>12</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>식재료 한 묶음 = N 끼 [임시]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>treat_minutes</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>60</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>의무실 치료(상태 이상 제거)에 걸리는 게임 분 [임시]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>affinity_start</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>20</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>시작 친밀도 0~100 [임시]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>affinity_talk</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>하루 첫 직접 대화 시 친밀도 + [임시]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>affinity_request</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>5</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>요청 수락 시 그 대원 친밀도 + [임시]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>liked_gift_mult</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>좋아하는 선물이면 친밀도 × [임시]</t>
         </is>
       </c>
     </row>
@@ -849,7 +1061,767 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>시설</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>종류</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>위치</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>높이</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>피로회복</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>체력회복</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>obj_bed_1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>b1_quarters</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>침대</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F2" t="n">
+        <v>12</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2층 침대 아래</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>obj_bed_2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>b1_quarters</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>침대</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2층 침대 위</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>obj_bed_3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>b1_quarters</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>침대</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>obj_bed_4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>b1_quarters</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>침대</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>obj_bed_5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>b1_quarters</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>침대</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>obj_bed_6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>b1_quarters</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>침대</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F7" t="n">
+        <v>11</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>obj_sofa_1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>f1_lounge</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>소파</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>공용실 소파 왼쪽</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>obj_sofa_2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>f1_lounge</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>소파</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F9" t="n">
+        <v>7</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>공용실 소파 오른쪽</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>obj_chair_o1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>f1_office</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>의자</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>행정실 책상 의자</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>obj_chair_o2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>f1_office</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>의자</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>obj_chair_m1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>f1_mess</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>의자</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>식당 의자</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>obj_chair_m2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>f1_mess</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>의자</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>obj_chair_m3</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>f1_mess</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>의자</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>obj_medbed_1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>b1_infirmary</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>의무침대</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G15" t="n">
+        <v>8</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>의무실 침대 (체력 회복)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>obj_medbed_2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>b1_infirmary</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>의무침대</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F16" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" t="n">
+        <v>8</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>obj_medbed_3</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>b1_infirmary</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>의무침대</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="C2:C200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"작업지시,외부의뢰"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C2:C200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"침대,소파,의자,의무침대"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>가격</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>친밀도</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>좋아하는 대원</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>gift_coffee</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>캔커피</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>npc_nikita</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>더미 선물</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>gift_choco</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>초콜릿</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>npc_alma, npc_hana</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>gift_gloves</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>가죽 장갑</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>npc_dan</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>gift_book</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>문고본</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>npc_ethan</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>gift_charm</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>행운 부적</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>npc_kira</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -968,75 +1940,67 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>출입(외부 의뢰 출발) / 계단(층 이동, 같은 칸 위아래 계단끼리 연결) / 행정 / 공용 / 생활 / 작업(제작·강화) / 훈련 / 미정</t>
+          <t>출입(외부 의뢰 출발) / 계단(층 이동, 같은 칸 위아래 계단끼리 연결) / 행정 / 공용 / 생활 / 식당(식재료) / 상점(PX 선물) / 의무(치료·체력 회복) / 무기고(강화·제작·장착) / 훈련 / 미정</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>시설</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>청소</t>
-        </is>
-      </c>
+          <t>오브젝트</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>O = 오염·청소 대상, 점검 점수에 들어감</t>
+          <t>침대·소파·의자·의무침대. 잠은 오브젝트 위에서만 피로 회복(피로회복/시간), 체력은 체력회복 &gt; 0 인 오브젝트(의무침대)에서만. 위치 = 방 폭 비율, 높이 = 눕는/앉는 높이 m</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>시설</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>조명</t>
-        </is>
-      </c>
+          <t>PX</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>방 조명 색 g1~g4 (전투 조명 프리셋과 같은 색 조합)</t>
+          <t>친밀도 선물: 가격(USD)·친밀도. 좋아하는 대원이면 × liked_gift_mult</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대원</t>
+          <t>시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>전투캐릭터</t>
+          <t>청소</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>밸런스 엑셀 캐릭터 시트 id — 훈련·장비 결과가 전투에 반영됨</t>
+          <t>O = 오염·청소 대상, 점검 점수에 들어감</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대원</t>
+          <t>시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>스프라이트</t>
+          <t>조명</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>assets/sprites/rig_&lt;스프라이트&gt;</t>
+          <t>방 조명 색 g1~g4 (전투 조명 프리셋과 같은 색 조합)</t>
         </is>
       </c>
     </row>
@@ -1048,108 +2012,142 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>일정</t>
+          <t>전투캐릭터</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>주간 일정은 data/outgame/schedules/&lt;대원 id&gt;.json — Godot 에디터 '일정' 탭</t>
+          <t>밸런스 엑셀 캐릭터 시트 id — 훈련·장비 결과가 전투에 반영됨</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>의뢰</t>
+          <t>대원</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>종류</t>
+          <t>스프라이트</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>작업지시(기지 안 시설에서 일함) / 외부의뢰(장소=정문, 나갔다가 복귀). 수익은 미지급으로 쌓였다가 주간 결산 때 지급</t>
+          <t>assets/sprites/rig_&lt;스프라이트&gt;</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>의뢰</t>
+          <t>대원</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>반복 / 처음부터</t>
+          <t>일정</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>반복 X = 한 번만 수락 가능. 처음부터 X = 요청 수락 등으로 열려야 보임</t>
+          <t>주간 일정은 data/outgame/schedules/&lt;대원 id&gt;.json — Godot 에디터 '일정' 탭</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대사</t>
+          <t>의뢰</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>id / 순서 / 화자</t>
+          <t>종류</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>같은 id 의 줄을 순서대로. 화자 = 대원 id (또는 아무 이름)</t>
+          <t>작업지시(기지 안 시설에서 일함) / 외부의뢰(장소=정문, 나갔다가 복귀). 수익은 미지급으로 쌓였다가 주간 결산 때 지급</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대화이벤트</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
+          <t>의뢰</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>반복 / 처음부터</t>
+        </is>
+      </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>두 대원이 같은 방에서 쉬는 중이면 대화(말풍선) → 클릭해 엿듣기. 장소 비우면 어디서나. 스토리 = 스토리 이벤트 id (있으면 '스토리' 표시)</t>
+          <t>반복 X = 한 번만 수락 가능. 처음부터 X = 요청 수락 등으로 열려야 보임</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>대사</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>수락효과</t>
+          <t>id / 순서 / 화자</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>의뢰:&lt;의뢰 id&gt; = 그 의뢰를 엶 / 비우면 효과 없음</t>
+          <t>같은 id 의 줄을 순서대로. 화자 = 대원 id (또는 아무 이름)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>대화이벤트</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>두 대원이 같은 방에서 쉬는 중이면 대화(말풍선) → 클릭해 엿듣기. 장소 비우면 어디서나. 스토리 = 스토리 이벤트 id (있으면 '스토리' 표시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>요청</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>수락효과</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>의뢰:&lt;의뢰 id&gt; = 그 의뢰를 엶 / 비우면 효과 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>제작</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>결과무기</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>밸런스 엑셀 아이템 시트 id. 비용·재료는 미정이라 시간만</t>
         </is>
@@ -1268,10 +2266,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
@@ -1281,7 +2279,7 @@
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1573,7 +2571,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>공용</t>
+          <t>식당</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1588,19 +2586,19 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>잠금 방 (더미)</t>
+          <t>달러로 식재료 공급, 식사하면 피로 감소</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>f1_stair_e</t>
+          <t>f1_px</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>동쪽 계단</t>
+          <t>PX</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1615,48 +2613,52 @@
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>상점</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>계단</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>g1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>g4</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>친밀도 선물 구매</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>b1_stair_w</t>
+          <t>f1_stair_e</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>서쪽 계단</t>
+          <t>동쪽 계단</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>b1</t>
+          <t>f1</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -1689,12 +2691,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>b1_quarters</t>
+          <t>b1_stair_w</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>숙소</t>
+          <t>서쪽 계단</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1703,10 +2705,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1718,34 +2720,30 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>생활</t>
+          <t>계단</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>g4</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>생활 구역 (더미)</t>
-        </is>
-      </c>
+          <t>g1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>b1_workshop</t>
+          <t>b1_quarters</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>작업실</t>
+          <t>숙소</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1754,7 +2752,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
         <v>2</v>
@@ -1769,7 +2767,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>작업</t>
+          <t>생활</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1779,24 +2777,24 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>g3</t>
+          <t>g4</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>무기 제작·강화 (더미)</t>
+          <t>침대 6 (잠자면 피로 회복)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>b1_training</t>
+          <t>b1_infirmary</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>훈련실</t>
+          <t>의무실</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1805,22 +2803,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
         <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>훈련</t>
+          <t>의무</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1830,24 +2828,24 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>g2</t>
+          <t>g1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>대원 훈련 (더미)</t>
+          <t>치료(상태 이상 제거)·휴식(체력 회복)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>b1_stair_e</t>
+          <t>b1_workshop</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>동쪽 계단</t>
+          <t>무기고</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1856,10 +2854,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1871,45 +2869,49 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>계단</t>
+          <t>무기고</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>g1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>g3</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>무기 강화·제작·장착 (id 는 이전 이름 그대로)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>b2_stair_w</t>
+          <t>b1_training</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>서쪽 계단</t>
+          <t>훈련실</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>b2</t>
+          <t>b1</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1918,81 +2920,81 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>계단</t>
+          <t>훈련</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>g1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>g2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>대원 훈련 (더미)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>b2_storage</t>
+          <t>b1_stair_e</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>창고</t>
+          <t>동쪽 계단</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>b2</t>
+          <t>b1</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>계단</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>X</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>공용</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>g4</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>잠금 방 (더미)</t>
-        </is>
-      </c>
+          <t>g1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>b2_sealed</t>
+          <t>b2_stair_w</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>봉쇄 구역</t>
+          <t>서쪽 계단</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2001,13 +3003,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2016,71 +3018,169 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>미정</t>
+          <t>계단</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>g2</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>잠금 방 (더미)</t>
-        </is>
-      </c>
+          <t>g1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>b2_storage</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>창고</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" t="n">
+        <v>120</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>공용</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>g4</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>잠금 방 (더미)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>b2_sealed</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>봉쇄 구역</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" t="n">
+        <v>200</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>g2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>잠금 방 (더미)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>b2_stair_e</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>동쪽 계단</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>b2</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>8</v>
-      </c>
-      <c r="E16" t="n">
+      <c r="D18" t="n">
+        <v>9</v>
+      </c>
+      <c r="E18" t="n">
         <v>1</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F18" t="n">
         <v>40</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>계단</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>g1</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="5">
@@ -2097,7 +3197,7 @@
       <formula1>"f1,b1,b2"</formula1>
     </dataValidation>
     <dataValidation sqref="H2:H200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"출입,계단,행정,공용,생활,작업,훈련,미정"</formula1>
+      <formula1>"출입,계단,행정,공용,생활,식당,상점,의무,무기고,훈련,미정"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2535,7 +3635,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>기지 안 업무 (더미)</t>
+          <t>무기고에서 일함 (더미)</t>
         </is>
       </c>
     </row>

--- a/data/outgame.xlsx
+++ b/data/outgame.xlsx
@@ -18,7 +18,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="제작" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="오브젝트" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PX" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="읽어보기" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="친밀도대화" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="읽어보기" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -436,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1032,21 +1033,6 @@
       <c r="C39" t="inlineStr">
         <is>
           <t>요청 수락 시 그 대원 친밀도 + [임시]</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>liked_gift_mult</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>2</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>좋아하는 선물이면 친밀도 × [임시]</t>
         </is>
       </c>
     </row>
@@ -1643,15 +1629,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1672,15 +1663,40 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>친밀도</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>좋아하는 대원</t>
+          <t>단</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>키라</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>이선</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>하나</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>앨마</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>니키타</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
@@ -1701,16 +1717,25 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="n">
         <v>3</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>npc_nikita</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>더미 선물</t>
+      <c r="G2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>니키타가 제일 좋아함 (더미)</t>
         </is>
       </c>
     </row>
@@ -1729,14 +1754,27 @@
         <v>8</v>
       </c>
       <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>npc_alma, npc_hana</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="n">
+        <v>9</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>하나·앨마가 좋아함</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1753,14 +1791,23 @@
         <v>20</v>
       </c>
       <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F4" t="n">
         <v>10</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>npc_dan</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>단이 제일 좋아함</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1777,14 +1824,27 @@
         <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>npc_ethan</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
       </c>
       <c r="F5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>13</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>이선이 제일 좋아함</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1801,14 +1861,58 @@
         <v>15</v>
       </c>
       <c r="D6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="n">
         <v>8</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>npc_kira</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>키라가 제일 좋아함</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>gift_canned</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>소시지 통조림</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>11</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>6</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>단이 좋아함</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1821,7 +1925,563 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>대원</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>친밀도</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>대사</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>aff_dan_30</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>npc_dan</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>30</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>d_aff_dan_30</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>더미 대사</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>aff_dan_50</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>npc_dan</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>50</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>d_aff_dan_50</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>aff_dan_70</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>npc_dan</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>70</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>d_aff_dan_70</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>aff_dan_90</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>npc_dan</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>90</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>d_aff_dan_90</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>aff_kira_30</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>npc_kira</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>d_aff_kira_30</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>aff_kira_50</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>npc_kira</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>d_aff_kira_50</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>aff_kira_70</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>npc_kira</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>70</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>d_aff_kira_70</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>aff_kira_90</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>npc_kira</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>90</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>d_aff_kira_90</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>aff_ethan_30</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>npc_ethan</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>30</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>d_aff_ethan_30</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>aff_ethan_50</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>npc_ethan</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>d_aff_ethan_50</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>aff_ethan_70</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>npc_ethan</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>70</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>d_aff_ethan_70</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>aff_ethan_90</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>npc_ethan</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>90</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>d_aff_ethan_90</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>aff_hana_30</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>npc_hana</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>30</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>d_aff_hana_30</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>aff_hana_50</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>npc_hana</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>50</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>d_aff_hana_50</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>aff_hana_70</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>npc_hana</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>70</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>d_aff_hana_70</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>aff_hana_90</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>npc_hana</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>90</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>d_aff_hana_90</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>aff_alma_30</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>npc_alma</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>30</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>d_aff_alma_30</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>aff_alma_50</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>npc_alma</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>50</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>d_aff_alma_50</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>aff_alma_70</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>npc_alma</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>70</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>d_aff_alma_70</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>aff_alma_90</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>npc_alma</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>90</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>d_aff_alma_90</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>aff_nikita_30</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>npc_nikita</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>30</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>d_aff_nikita_30</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>aff_nikita_50</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>npc_nikita</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>50</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>d_aff_nikita_50</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>aff_nikita_70</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>npc_nikita</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>70</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>d_aff_nikita_70</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>aff_nikita_90</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>npc_nikita</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>90</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>d_aff_nikita_90</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1963,27 +2623,31 @@
           <t>PX</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>기본 / 대원 이름 열</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>친밀도 선물: 가격(USD)·친밀도. 좋아하는 대원이면 × liked_gift_mult</t>
+          <t>친밀도 선물: 가격(USD). 대원 이름 열 = 그 대원에게 줄 때 오르는 친밀도 (빈 칸 = 기본). 기본보다 크면 좋아함(2배 이상 = 아주 좋아함), 작으면 별로</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>시설</t>
+          <t>친밀도대화</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>청소</t>
+          <t>친밀도 / 대사</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>O = 오염·청소 대상, 점검 점수에 들어감</t>
+          <t>그 대원 친밀도가 기준 이상이면 해금 → 클릭해 대화하면 안 본 대화부터, 다 봤으면 해금된 가장 높은 단계. 머리 위 ♥ = 새 대화</t>
         </is>
       </c>
     </row>
@@ -1995,29 +2659,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>조명</t>
+          <t>청소</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>방 조명 색 g1~g4 (전투 조명 프리셋과 같은 색 조합)</t>
+          <t>O = 오염·청소 대상, 점검 점수에 들어감</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대원</t>
+          <t>시설</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>전투캐릭터</t>
+          <t>조명</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>밸런스 엑셀 캐릭터 시트 id — 훈련·장비 결과가 전투에 반영됨</t>
+          <t>방 조명 색 g1~g4 (전투 조명 프리셋과 같은 색 조합)</t>
         </is>
       </c>
     </row>
@@ -2029,12 +2693,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>스프라이트</t>
+          <t>전투캐릭터</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>assets/sprites/rig_&lt;스프라이트&gt;</t>
+          <t>밸런스 엑셀 캐릭터 시트 id — 훈련·장비 결과가 전투에 반영됨</t>
         </is>
       </c>
     </row>
@@ -2046,29 +2710,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>일정</t>
+          <t>스프라이트</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>주간 일정은 data/outgame/schedules/&lt;대원 id&gt;.json — Godot 에디터 '일정' 탭</t>
+          <t>assets/sprites/rig_&lt;스프라이트&gt;</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>의뢰</t>
+          <t>대원</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>종류</t>
+          <t>일정</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>작업지시(기지 안 시설에서 일함) / 외부의뢰(장소=정문, 나갔다가 복귀). 수익은 미지급으로 쌓였다가 주간 결산 때 지급</t>
+          <t>주간 일정은 data/outgame/schedules/&lt;대원 id&gt;.json — Godot 에디터 '일정' 탭</t>
         </is>
       </c>
     </row>
@@ -2080,74 +2744,91 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>반복 / 처음부터</t>
+          <t>종류</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>반복 X = 한 번만 수락 가능. 처음부터 X = 요청 수락 등으로 열려야 보임</t>
+          <t>작업지시(기지 안 시설에서 일함) / 외부의뢰(장소=정문, 나갔다가 복귀). 수익은 미지급으로 쌓였다가 주간 결산 때 지급</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대사</t>
+          <t>의뢰</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>id / 순서 / 화자</t>
+          <t>반복 / 처음부터</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>같은 id 의 줄을 순서대로. 화자 = 대원 id (또는 아무 이름)</t>
+          <t>반복 X = 한 번만 수락 가능. 처음부터 X = 요청 수락 등으로 열려야 보임</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대화이벤트</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
+          <t>대사</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>id / 순서 / 화자</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>두 대원이 같은 방에서 쉬는 중이면 대화(말풍선) → 클릭해 엿듣기. 장소 비우면 어디서나. 스토리 = 스토리 이벤트 id (있으면 '스토리' 표시)</t>
+          <t>같은 id 의 줄을 순서대로. 화자 = 대원 id (또는 아무 이름)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>요청</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>수락효과</t>
-        </is>
-      </c>
+          <t>대화이벤트</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>의뢰:&lt;의뢰 id&gt; = 그 의뢰를 엶 / 비우면 효과 없음</t>
+          <t>두 대원이 같은 방에서 쉬는 중이면 대화(말풍선) → 클릭해 엿듣기. 장소 비우면 어디서나. 스토리 = 스토리 이벤트 id (있으면 '스토리' 표시)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>요청</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>수락효과</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>의뢰:&lt;의뢰 id&gt; = 그 의뢰를 엶 / 비우면 효과 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>제작</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>결과무기</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>밸런스 엑셀 아이템 시트 id. 비용·재료는 미정이라 시간만</t>
         </is>
@@ -3747,7 +4428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4115,6 +4796,486 @@
       <c r="D18" t="inlineStr">
         <is>
           <t>[요청 테스트] 확인 감사합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>d_aff_dan_30</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>npc_dan</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>[친밀도 30 대화] 요즘 기지 분위기 나쁘지 않네요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>d_aff_dan_50</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>npc_dan</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>[친밀도 50 대화] 예전 부대 얘기, 언젠가 해 드리죠.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>d_aff_dan_70</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>npc_dan</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>[친밀도 70 대화] 지휘관님 등은 제가 지킵니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>d_aff_dan_90</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>npc_dan</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>[친밀도 90 대화] …고맙습니다. 여기가 집 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>d_aff_kira_30</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>npc_kira</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>[친밀도 30 대화] 일정표, 지휘관님 것도 정리해 뒀어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>d_aff_kira_50</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>npc_kira</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>[친밀도 50 대화] 부적 같은 거 믿진 않지만… 고마워요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>d_aff_kira_70</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>npc_kira</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>[친밀도 70 대화] 저, 사실 겁이 많아요. 비밀이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>d_aff_kira_90</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>npc_kira</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>[친밀도 90 대화] 끝까지 같이 가요, 지휘관님.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>d_aff_ethan_30</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>npc_ethan</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>[친밀도 30 대화] 무기고 정리는 제 담당이죠.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>d_aff_ethan_50</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>npc_ethan</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>[친밀도 50 대화] 이 책, 다 읽으면 빌려 드릴게요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>d_aff_ethan_70</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>npc_ethan</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>[친밀도 70 대화] 지하 2층… 조금 더 알아봤어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>d_aff_ethan_90</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>npc_ethan</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>[친밀도 90 대화] 지휘관님이라면 믿을 수 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>d_aff_hana_30</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>npc_hana</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>[친밀도 30 대화] 오늘도 무사히 끝났네요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>d_aff_hana_50</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>npc_hana</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>[친밀도 50 대화] 단 거 먹으면 기운이 나요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>d_aff_hana_70</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>npc_hana</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>[친밀도 70 대화] 가끔은 같이 쉬어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>d_aff_hana_90</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>npc_hana</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>[친밀도 90 대화] 지휘관님 덕분에 버텨요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>d_aff_alma_30</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>npc_alma</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>[친밀도 30 대화] 다친 데 없죠? 확인할게요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>d_aff_alma_50</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>npc_alma</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>[친밀도 50 대화] 의무실 커튼 색, 바꿔도 될까요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>d_aff_alma_70</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>npc_alma</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>[친밀도 70 대화] 사실 피 보는 거 아직도 무서워요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>d_aff_alma_90</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>npc_alma</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>[친밀도 90 대화] 모두 살아서 돌아오게 할게요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>d_aff_nikita_30</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>npc_nikita</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>[친밀도 30 대화] 관측 기록, 이상 없음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>d_aff_nikita_50</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>npc_nikita</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>[친밀도 50 대화] 커피… 고마워요. 이건 진짜예요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>d_aff_nikita_70</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>npc_nikita</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>[친밀도 70 대화] 별 보는 거 좋아해요. 기지 위에서.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>d_aff_nikita_90</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>npc_nikita</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>[친밀도 90 대화] 제 기록에 지휘관님 이름, 꼭 남길게요.</t>
         </is>
       </c>
     </row>

--- a/data/outgame.xlsx
+++ b/data/outgame.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -829,208 +829,238 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>run_speed_mult</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2048</v>
+        <v>2.2</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>오염·점검 날짜 난수 시드 [임시]</t>
+          <t>더블클릭으로 보낸 대원이 뛰는 속도 = 걷기 × [임시]</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>fatigue_start</t>
+          <t>fatigue_run_per_hour</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>시작 피로도 0~100 (높을수록 피곤) [임시]</t>
+          <t>뛰는 동안 시간당 피로 증가 [임시]</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>fatigue_awake_per_hour</t>
+          <t>seed</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>2048</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>깨어 있을 때 시간당 피로 증가 [임시]</t>
+          <t>오염·점검 날짜 난수 시드 [임시]</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>fatigue_work_per_hour</t>
+          <t>fatigue_start</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>업무·청소·지시 중 시간당 피로 증가 [임시]</t>
+          <t>시작 피로도 0~100 (높을수록 피곤) [임시]</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>fatigue_train_per_hour</t>
+          <t>fatigue_awake_per_hour</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>훈련 중 시간당 피로 증가 [임시]</t>
+          <t>깨어 있을 때 시간당 피로 증가 [임시]</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>fatigue_battle</t>
+          <t>fatigue_work_per_hour</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>전투 한 번 참가 시 피로 증가 [임시]</t>
+          <t>업무·청소·지시 중 시간당 피로 증가 [임시]</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>hungry_fatigue</t>
+          <t>fatigue_train_per_hour</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>식사 시간에 식재료가 없으면 피로 증가 [임시]</t>
+          <t>훈련 중 시간당 피로 증가 [임시]</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>food_start</t>
+          <t>fatigue_battle</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>시작 식재료 (1 = 한 끼) [임시]</t>
+          <t>전투 한 번 참가 시 피로 증가 [임시]</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>food_pack_price</t>
+          <t>hungry_fatigue</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>식재료 한 묶음 가격 USD [임시]</t>
+          <t>식사 시간에 식재료가 없으면 피로 증가 [임시]</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>food_pack_amount</t>
+          <t>food_start</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>식재료 한 묶음 = N 끼 [임시]</t>
+          <t>시작 식재료 (1 = 한 끼) [임시]</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>treat_minutes</t>
+          <t>food_pack_price</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>의무실 치료(상태 이상 제거)에 걸리는 게임 분 [임시]</t>
+          <t>식재료 한 묶음 가격 USD [임시]</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>affinity_start</t>
+          <t>food_pack_amount</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>시작 친밀도 0~100 [임시]</t>
+          <t>식재료 한 묶음 = N 끼 [임시]</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>affinity_talk</t>
+          <t>treat_minutes</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>하루 첫 직접 대화 시 친밀도 + [임시]</t>
+          <t>의무실 치료(상태 이상 제거)에 걸리는 게임 분 [임시]</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>affinity_start</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>20</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>시작 친밀도 0~100 [임시]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>affinity_talk</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>하루 첫 직접 대화 시 친밀도 + [임시]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>affinity_request</t>
         </is>
       </c>
-      <c r="B39" t="n">
+      <c r="B41" t="n">
         <v>5</v>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>요청 수락 시 그 대원 친밀도 + [임시]</t>
         </is>
@@ -2715,7 +2745,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>assets/sprites/rig_&lt;스프라이트&gt;</t>
+          <t>assets/characters/&lt;스프라이트&gt;/ — 캐릭터 프레임 애니메이션 (tools/char_sprites.py)</t>
         </is>
       </c>
     </row>

--- a/data/outgame.xlsx
+++ b/data/outgame.xlsx
@@ -16,10 +16,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="대화이벤트" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요청" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="제작" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="오브젝트" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PX" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="친밀도대화" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="읽어보기" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연구" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="오브젝트" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PX" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="친밀도대화" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="읽어보기" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -42,7 +43,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -52,6 +53,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002E3440"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002F4F6F"/>
       </patternFill>
     </fill>
   </fills>
@@ -67,11 +73,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -437,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1063,6 +1070,23 @@
       <c r="C41" t="inlineStr">
         <is>
           <t>요청 수락 시 그 대원 친밀도 + [임시]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>researcher_npc</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>npc_rohan</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>연구원 대원 id — 클릭하면 연구 창, 이 대원이 연구실(기능=연구)에서 깨어 있을 때만 연구가 진행됨 [임시]</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1101,217 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>해금제작</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>소요(분)</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>선행연구</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>res_shotgun</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>산탄총 설계</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>r_shotgun</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>60</v>
+      </c>
+      <c r="E2" t="n">
+        <v>180</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>가까운 적에게 강한 원거리 무기 (더미)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>res_smg</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>기관단총 설계</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>r_smg</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>80</v>
+      </c>
+      <c r="E3" t="n">
+        <v>240</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>가벼운 연사 무기 (더미)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>res_blade</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>고주파 블레이드</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>r_blade</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="n">
+        <v>300</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>근접 위력 최고 (더미)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>res_mg</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>경기관총 설계</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>r_mg</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>150</v>
+      </c>
+      <c r="E5" t="n">
+        <v>360</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>res_smg</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>기관단총 연구 후 (더미)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>res_launcher</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>유탄발사기 설계</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>r_launcher</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>200</v>
+      </c>
+      <c r="E6" t="n">
+        <v>480</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>res_shotgun</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>산탄총 연구 후 (더미)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1228,7 +1462,6 @@
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1258,7 +1491,6 @@
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1288,7 +1520,6 @@
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1318,7 +1549,6 @@
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1450,7 +1680,6 @@
       <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1514,7 +1743,6 @@
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1544,7 +1772,6 @@
       <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1608,7 +1835,6 @@
       <c r="G16" t="n">
         <v>8</v>
       </c>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1638,7 +1864,74 @@
       <c r="G17" t="n">
         <v>8</v>
       </c>
-      <c r="H17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>obj_chair_l1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>b1_lab</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>의자</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>연구실 책상 의자</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>obj_cot_lab</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>b1_lab</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>침대</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F19" t="n">
+        <v>10</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>연구실 간이침대 (로한은 여기서 잠)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -1653,7 +1946,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1749,14 +2042,12 @@
       <c r="D2" t="n">
         <v>2</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
         <v>3</v>
       </c>
       <c r="G2" t="n">
         <v>4</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
         <v>1</v>
       </c>
@@ -1792,14 +2083,12 @@
       <c r="F3" t="n">
         <v>5</v>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>12</v>
       </c>
       <c r="I3" t="n">
         <v>9</v>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>하나·앨마가 좋아함</t>
@@ -1829,10 +2118,6 @@
       <c r="F4" t="n">
         <v>10</v>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>단이 제일 좋아함</t>
@@ -1859,11 +2144,9 @@
       <c r="E5" t="n">
         <v>2</v>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
         <v>13</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
         <v>6</v>
       </c>
@@ -1893,16 +2176,12 @@
       <c r="D6" t="n">
         <v>4</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
         <v>14</v>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>8</v>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>키라가 제일 좋아함</t>
@@ -1929,12 +2208,9 @@
       <c r="E7" t="n">
         <v>11</v>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
         <v>6</v>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
         <v>1</v>
       </c>
@@ -1949,13 +2225,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2036,7 +2312,6 @@
           <t>d_aff_dan_50</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2057,7 +2332,6 @@
           <t>d_aff_dan_70</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2078,7 +2352,6 @@
           <t>d_aff_dan_90</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2099,7 +2372,6 @@
           <t>d_aff_kira_30</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2120,7 +2392,6 @@
           <t>d_aff_kira_50</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2141,7 +2412,6 @@
           <t>d_aff_kira_70</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2162,7 +2432,6 @@
           <t>d_aff_kira_90</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2183,7 +2452,6 @@
           <t>d_aff_ethan_30</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2204,7 +2472,6 @@
           <t>d_aff_ethan_50</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2225,7 +2492,6 @@
           <t>d_aff_ethan_70</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2246,7 +2512,6 @@
           <t>d_aff_ethan_90</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2267,7 +2532,6 @@
           <t>d_aff_hana_30</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2288,7 +2552,6 @@
           <t>d_aff_hana_50</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2309,7 +2572,6 @@
           <t>d_aff_hana_70</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2330,7 +2592,6 @@
           <t>d_aff_hana_90</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2351,7 +2612,6 @@
           <t>d_aff_alma_30</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2372,7 +2632,6 @@
           <t>d_aff_alma_50</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2393,7 +2652,6 @@
           <t>d_aff_alma_70</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2414,7 +2672,6 @@
           <t>d_aff_alma_90</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2435,7 +2692,6 @@
           <t>d_aff_nikita_30</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2456,7 +2712,6 @@
           <t>d_aff_nikita_50</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2477,7 +2732,6 @@
           <t>d_aff_nikita_70</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2498,20 +2752,99 @@
           <t>d_aff_nikita_90</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>aff_rohan_30</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>npc_rohan</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>30</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>d_aff_rohan_30</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>aff_rohan_50</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>npc_rohan</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>50</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>d_aff_rohan_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>aff_rohan_70</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>npc_rohan</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>70</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>d_aff_rohan_70</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>aff_rohan_90</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>npc_rohan</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>90</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>d_aff_rohan_90</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2542,7 +2875,6 @@
           <t>공통</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>모든 수치·이름·대사는 프로토타입 임시값/더미 (01_OUTGAME_GDD 13절 미정 항목). 게임 실행 중 저장하면 1초 안에 다시 읽음</t>
@@ -2640,7 +2972,6 @@
           <t>오브젝트</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>침대·소파·의자·의무침대. 잠은 오브젝트 위에서만 피로 회복(피로회복/시간), 체력은 체력회복 &gt; 0 인 오브젝트(의무침대)에서만. 위치 = 방 폭 비율, 높이 = 눕는/앉는 높이 m</t>
@@ -2823,7 +3154,6 @@
           <t>대화이벤트</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>두 대원이 같은 방에서 쉬는 중이면 대화(말풍선) → 클릭해 엿듣기. 장소 비우면 어디서나. 스토리 = 스토리 이벤트 id (있으면 '스토리' 표시)</t>
@@ -2861,6 +3191,57 @@
       <c r="C21" t="inlineStr">
         <is>
           <t>밸런스 엑셀 아이템 시트 id. 비용·재료는 미정이라 시간만</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>시설</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>기능=연구</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>연구실. 연구원(설정 researcher_npc)을 클릭하면 연구 창</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>대원</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>전투캐릭터 (비움)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>비우면 전투에 나가지 않는 대원 (로한 — 연구원). 체력 게이지 없음, 출정 대기 목록에 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>연구</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>해금제작 / 비용 / 소요(분) / 선행연구</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>연구 완료 → 해금제작(제작 시트 id, 쉼표로 여럿)이 무기고에서 제작 가능. 어떤 연구에도 없는 레시피는 처음부터 가능. 비용은 시작할 때 달러로, 한 번에 하나, 연구원이 연구실에서 깨어 있을 때만 진행</t>
         </is>
       </c>
     </row>
@@ -2977,7 +3358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3146,7 +3527,6 @@
           <t>g1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3397,7 +3777,6 @@
           <t>g1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3444,7 +3823,6 @@
           <t>g1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3695,7 +4073,6 @@
           <t>g1</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3742,7 +4119,6 @@
           <t>g1</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3891,7 +4267,57 @@
           <t>g1</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>b1_lab</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>연구실</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>연구</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>g4</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>로한이 일하는 곳 — 로한을 클릭하면 새 무기 연구 (지하 1층 서쪽 끝)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="5">
@@ -3921,7 +4347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4010,7 +4436,6 @@
           <t>d_talk_dan</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4046,7 +4471,6 @@
           <t>d_talk_kira</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4082,7 +4506,6 @@
           <t>d_talk_ethan</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4118,7 +4541,6 @@
           <t>d_talk_hana</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4154,7 +4576,6 @@
           <t>d_talk_alma</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4190,7 +4611,41 @@
           <t>d_talk_nikita</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>npc_rohan</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>로한</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>rohan</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>178</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>b1_lab</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>d_talk_rohan</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>연구원 — 전투에 나가지 않음. 클릭하면 무기 연구</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4458,7 +4913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5306,6 +5761,126 @@
       <c r="D42" t="inlineStr">
         <is>
           <t>[친밀도 90 대화] 제 기록에 지휘관님 이름, 꼭 남길게요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>d_talk_rohan</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>npc_rohan</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>아, 지휘관님. 마침 설계도 하나 봐 주실래요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>d_talk_rohan</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>npc_rohan</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>재료랑 돈만 있으면 뭐든 만들어 보죠.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>d_aff_rohan_30</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>npc_rohan</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>[친밀도 30 대화] 커피는 블랙. 연구원의 기본이죠.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>d_aff_rohan_50</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>npc_rohan</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>[친밀도 50 대화] 이 기지 발전기, 제가 몰래 손봤어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>d_aff_rohan_70</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>npc_rohan</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>[친밀도 70 대화] 사실 전에 있던 연구소는… 말하기 싫네요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>d_aff_rohan_90</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>npc_rohan</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>[친밀도 90 대화] 지휘관님 무기엔 제 이름 새겨 둘게요.</t>
         </is>
       </c>
     </row>
@@ -5403,20 +5978,17 @@
           <t>npc_kira</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>d_conv_01</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
         <v>3</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>일반 대화 (엿듣기 검증용 더미)</t>
@@ -5439,20 +6011,17 @@
           <t>npc_nikita</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>d_conv_02</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
         <v>3</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>일반 대화 (더미)</t>
@@ -5475,7 +6044,6 @@
           <t>npc_alma</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>d_conv_story_01</t>
@@ -5492,7 +6060,6 @@
       <c r="H4" t="n">
         <v>5</v>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>스토리 관련 대화 검증용 더미 (6.3절)</t>
@@ -5622,7 +6189,6 @@
           <t>d_req_02_ok</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>보상 없는 확인 요청 (더미)</t>
@@ -5640,7 +6206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5721,7 +6287,6 @@
       <c r="D3" t="n">
         <v>180</v>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5742,7 +6307,6 @@
       <c r="D4" t="n">
         <v>240</v>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5763,7 +6327,131 @@
       <c r="D5" t="n">
         <v>240</v>
       </c>
-      <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>r_shotgun</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>산탄총 제작</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>shotgun</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>240</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>연구: 산탄총 설계</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>r_smg</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>기관단총 제작</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>smg</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>240</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>연구: 기관단총 설계</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>r_blade</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>고주파 블레이드 제작</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>blade</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>300</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>연구: 고주파 블레이드</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>r_mg</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>경기관총 제작</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>360</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>연구: 경기관총 (기관단총 다음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>r_launcher</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>유탄발사기 제작</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>launcher</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>420</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>연구: 유탄발사기 (산탄총 다음)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/outgame.xlsx
+++ b/data/outgame.xlsx
@@ -4629,7 +4629,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>

--- a/data/outgame.xlsx
+++ b/data/outgame.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1087,6 +1087,81 @@
       <c r="C42" t="inlineStr">
         <is>
           <t>연구원 대원 id — 클릭하면 연구 창, 이 대원이 연구실(기능=연구)에서 깨어 있을 때만 연구가 진행됨 [임시]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>xp_win</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>100</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>전투 승리 시 출전 대원 경험치 [임시]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>xp_lose</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>40</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>전투 패배 시 출전 대원 경험치 [임시]</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>xp_level_base</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>100</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>다음 레벨까지 필요 경험치 = base + step × (지금 레벨 - 시작 레벨) [임시]</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>xp_level_step</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>50</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>(위 공식의 step) [임시]</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>level_max</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>20</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>최대 레벨 [임시]</t>
         </is>
       </c>
     </row>

--- a/data/outgame.xlsx
+++ b/data/outgame.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1162,6 +1162,21 @@
       <c r="C47" t="inlineStr">
         <is>
           <t>최대 레벨 [임시]</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>faith_battle</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>5</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>전투에 출전할 때마다 신앙도 + [임시]</t>
         </is>
       </c>
     </row>
